--- a/05-kpi-dashboard-3-sources/output/kpi_dashboard.xlsx
+++ b/05-kpi-dashboard-3-sources/output/kpi_dashboard.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>paweł.kaminska43@example.com</t>
+          <t>pawel.kaminska43@example.com</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>paweł.wojcik1@example.com</t>
+          <t>pawel.wojcik1@example.com</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>michał.szymanski2@example.com</t>
+          <t>michal.szymanski2@example.com</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>paweł.wojcik25@example.com</t>
+          <t>pawel.wojcik25@example.com</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>paweł.jankowska46@example.com</t>
+          <t>pawel.jankowska46@example.com</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
